--- a/output/見積書_雛形.xlsx
+++ b/output/見積書_雛形.xlsx
@@ -116,7 +116,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -145,7 +145,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -156,7 +156,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -165,10 +165,10 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -177,7 +177,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -573,10 +573,10 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　　　　　 様</t>
+          <t>様</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -587,7 +587,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="20" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>下記の通り御見積申し上げます。何卒ご用命賜りますようお願い申し上げます。</t>
@@ -601,24 +601,24 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>E36</f>
+        <f>E34</f>
         <v/>
       </c>
       <c r="C6" s="9" t="n"/>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>（消費税込）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>（税込）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
       <c r="E7" s="11" t="inlineStr">
         <is>
           <t>株式会社ホームクレバー</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="26" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
           <t>工事名称</t>
@@ -627,13 +627,18 @@
       <c r="B8" s="13" t="inlineStr"/>
       <c r="C8" s="9" t="n"/>
       <c r="D8" s="9" t="n"/>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>代表取締役　都築 光正</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>代表取締役　都築 光正
+〒275-0016 千葉県習志野市津田沼5-10-1
+TEL 047-453-0050 FAX 047-453-0070
+建設業許可 千葉県知事許可（般-6）第53280号
+宅地建物取引業 千葉県知事（5）第14825号
+登録番号 T9040001015043</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
           <t>工事場所</t>
@@ -642,13 +647,8 @@
       <c r="B9" s="13" t="inlineStr"/>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="9" t="n"/>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>〒275-0016 千葉県習志野市津田沼5-10-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
+    </row>
+    <row r="10" ht="26" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
           <t>工期</t>
@@ -661,13 +661,8 @@
       </c>
       <c r="C10" s="9" t="n"/>
       <c r="D10" s="9" t="n"/>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>TEL 047-453-0050 FAX 047-453-0070</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
+    </row>
+    <row r="11" ht="26" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
           <t>お支払い条件</t>
@@ -680,13 +675,8 @@
       </c>
       <c r="C11" s="9" t="n"/>
       <c r="D11" s="9" t="n"/>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>建設業許可 千葉県知事許可（般-6）第53280号</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
+    </row>
+    <row r="12" ht="26" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
           <t>有効期限</t>
@@ -699,66 +689,70 @@
       </c>
       <c r="C12" s="9" t="n"/>
       <c r="D12" s="9" t="n"/>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>宅地建物取引業 千葉県知事（5）第14825号</t>
-        </is>
-      </c>
     </row>
     <row r="13">
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>登録番号 T9040001015043</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>担当：営業部　都築 将太郎</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>名称・内訳</t>
         </is>
       </c>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>金額（税抜）</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr"/>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="18">
-        <f>SUM(E19:E22)</f>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="18">
+        <f>SUM(E17:E20)</f>
         <v/>
       </c>
-      <c r="F18" s="17" t="n"/>
-    </row>
-    <row r="19">
+      <c r="F16" s="17" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="19" t="inlineStr"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="20" t="inlineStr"/>
+      <c r="D17" s="20" t="inlineStr"/>
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="22" t="inlineStr"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="19" t="inlineStr"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="20" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="21" t="n"/>
+      <c r="F18" s="22" t="inlineStr"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="19" t="inlineStr"/>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="20" t="inlineStr"/>
@@ -766,7 +760,7 @@
       <c r="E19" s="21" t="n"/>
       <c r="F19" s="22" t="inlineStr"/>
     </row>
-    <row r="20">
+    <row r="20" ht="18" customHeight="1">
       <c r="A20" s="19" t="inlineStr"/>
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="20" t="inlineStr"/>
@@ -775,14 +769,17 @@
       <c r="F20" s="22" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr"/>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="20" t="inlineStr"/>
-      <c r="D21" s="20" t="inlineStr"/>
-      <c r="E21" s="21" t="n"/>
-      <c r="F21" s="22" t="inlineStr"/>
-    </row>
-    <row r="22">
+      <c r="A21" s="16" t="inlineStr"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="18">
+        <f>SUM(E22:E25)</f>
+        <v/>
+      </c>
+      <c r="F21" s="17" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
       <c r="A22" s="19" t="inlineStr"/>
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="20" t="inlineStr"/>
@@ -790,18 +787,15 @@
       <c r="E22" s="21" t="n"/>
       <c r="F22" s="22" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr"/>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="18">
-        <f>SUM(E24:E27)</f>
-        <v/>
-      </c>
-      <c r="F23" s="17" t="n"/>
-    </row>
-    <row r="24">
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="19" t="inlineStr"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="20" t="inlineStr"/>
+      <c r="D23" s="20" t="inlineStr"/>
+      <c r="E23" s="21" t="n"/>
+      <c r="F23" s="22" t="inlineStr"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
       <c r="A24" s="19" t="inlineStr"/>
       <c r="B24" s="9" t="n"/>
       <c r="C24" s="20" t="inlineStr"/>
@@ -809,7 +803,7 @@
       <c r="E24" s="21" t="n"/>
       <c r="F24" s="22" t="inlineStr"/>
     </row>
-    <row r="25">
+    <row r="25" ht="18" customHeight="1">
       <c r="A25" s="19" t="inlineStr"/>
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="20" t="inlineStr"/>
@@ -818,40 +812,60 @@
       <c r="F25" s="22" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr"/>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="20" t="inlineStr"/>
-      <c r="D26" s="20" t="inlineStr"/>
-      <c r="E26" s="21" t="n"/>
-      <c r="F26" s="22" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr"/>
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>共通費</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="18">
+        <f>SUM(E27:E30)</f>
+        <v/>
+      </c>
+      <c r="F26" s="17" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>養生費</t>
+        </is>
+      </c>
       <c r="B27" s="9" t="n"/>
-      <c r="C27" s="20" t="inlineStr"/>
-      <c r="D27" s="20" t="inlineStr"/>
+      <c r="C27" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>式</t>
+        </is>
+      </c>
       <c r="E27" s="21" t="n"/>
       <c r="F27" s="22" t="inlineStr"/>
     </row>
-    <row r="28">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>共通費</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="n"/>
-      <c r="C28" s="17" t="n"/>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="18">
-        <f>SUM(E29:E32)</f>
-        <v/>
-      </c>
-      <c r="F28" s="17" t="n"/>
-    </row>
-    <row r="29">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>現場管理費</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>式</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="n"/>
+      <c r="F28" s="22" t="inlineStr"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>養生費</t>
+          <t>一般管理費</t>
         </is>
       </c>
       <c r="B29" s="9" t="n"/>
@@ -866,10 +880,10 @@
       <c r="E29" s="21" t="n"/>
       <c r="F29" s="22" t="inlineStr"/>
     </row>
-    <row r="30">
+    <row r="30" ht="18" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>現場管理費</t>
+          <t>法定福利費</t>
         </is>
       </c>
       <c r="B30" s="9" t="n"/>
@@ -884,160 +898,119 @@
       <c r="E30" s="21" t="n"/>
       <c r="F30" s="22" t="inlineStr"/>
     </row>
-    <row r="31">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>一般管理費</t>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>小計</t>
         </is>
       </c>
       <c r="B31" s="9" t="n"/>
-      <c r="C31" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="20" t="inlineStr">
-        <is>
-          <t>式</t>
-        </is>
-      </c>
-      <c r="E31" s="21" t="n"/>
-      <c r="F31" s="22" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>法定福利費</t>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="24">
+        <f>E16+E21+E26</f>
+        <v/>
+      </c>
+      <c r="F31" s="9" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>消費税（10%）</t>
         </is>
       </c>
       <c r="B32" s="9" t="n"/>
-      <c r="C32" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="20" t="inlineStr">
-        <is>
-          <t>式</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="n"/>
-      <c r="F32" s="22" t="inlineStr"/>
-    </row>
-    <row r="33">
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="24">
+        <f>ROUNDDOWN(E31*10/100,0)</f>
+        <v/>
+      </c>
+      <c r="F32" s="9" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
       <c r="A33" s="23" t="inlineStr">
         <is>
-          <t>小計</t>
+          <t>端数値引き</t>
         </is>
       </c>
       <c r="B33" s="9" t="n"/>
       <c r="C33" s="9" t="n"/>
       <c r="D33" s="9" t="n"/>
-      <c r="E33" s="24">
-        <f>E18+E23+E28</f>
+      <c r="E33" s="25">
+        <f>MOD(E31+E32,1000)</f>
         <v/>
       </c>
       <c r="F33" s="9" t="n"/>
     </row>
-    <row r="34">
-      <c r="A34" s="23" t="inlineStr">
-        <is>
-          <t>消費税（10%）</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="n"/>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="24">
-        <f>ROUNDDOWN(E33*10/100,0)</f>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t>合計（税込）</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="27">
+        <f>E31+E32-E33</f>
         <v/>
       </c>
-      <c r="F34" s="9" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>端数値引き</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="25">
-        <f>MOD(E33+E34,1000)</f>
-        <v/>
-      </c>
-      <c r="F35" s="9" t="n"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>合計（税込）</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="n"/>
-      <c r="C36" s="15" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="27">
-        <f>E33+E34-E35</f>
-        <v/>
-      </c>
-      <c r="F36" s="15" t="n"/>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="28" t="inlineStr">
+      <c r="F34" s="15" t="n"/>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>※ 工事期間中の電気・水道はお客様宅のものを使用させていただきます。</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="28" t="inlineStr">
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>※ 上記以外の工事は別途となります。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="34">
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E12:F12"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A15:B15"/>
     <mergeCell ref="B8:D8"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E8:F12"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A27:B27"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A21:B21"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A32:B32"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>